--- a/excel/universities/university-of-turku.xlsx
+++ b/excel/universities/university-of-turku.xlsx
@@ -115,7 +115,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.utu.fi/en/study-at-utu/apply</t>
+          <t xml:space="preserve">https://www.utu.fi/en/study-at-utu/apply-to-masters-programmes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -125,27 +125,27 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t xml:space="preserve">International master's degree programmes</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Autumn</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Autumn</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Programme-specific</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fill program-specific information here</t>
+          <t xml:space="preserve">The next application round for autumn 2026 intake was 2026-01-07 to 2026-01-21 with attachments due 2026-01-28.</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -229,37 +229,37 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t xml:space="preserve">International master's degree programmes</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Autumn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-07</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-21</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Autumn</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.utu.fi/en/study-at-utu/apply</t>
+          <t xml:space="preserve">https://www.utu.fi/en/study-at-utu/apply-to-masters-programmes</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify annual deadlines</t>
+          <t xml:space="preserve">Attachment deadline 2026-01-28; results published 2026-03-26.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -275,7 +275,7 @@
 
 <file path=xl\worksheets\sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -333,30 +333,198 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">International master's degree programmes</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Passport</t>
+          <t xml:space="preserve">Degree certificate</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t xml:space="preserve">If graduated</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Attach scans of original degree certificate and official translation if needed.</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.utu.fi/en/study-at-utu/apply-to-masters-programmes</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Turku</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">International master's degree programmes</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transcript of records</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.utu.fi/en/study-at-utu/apply</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Most recent transcript is accepted if the applicant has not yet graduated.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.utu.fi/en/study-at-utu/apply-to-masters-programmes</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Turku</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">International master's degree programmes</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proof of language skills</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Language proof options are listed on the UTU language requirements page referenced from the application guide.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.utu.fi/en/study-at-utu/apply-to-masters-programmes</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Turku</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">International master's degree programmes</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Passport or identity card</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Residence permit card also required if applying for fee exemption based on permit.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.utu.fi/en/study-at-utu/apply-to-masters-programmes</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Turku</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">International master's degree programmes</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Programme-specific documents</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check programme</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Examples include motivation letters self-introduction videos or other programme-specific materials.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.utu.fi/en/study-at-utu/apply-to-masters-programmes</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-03-14</t>
         </is>
@@ -369,7 +537,7 @@
 
 <file path=xl\worksheets\sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -420,15 +588,30 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">citation_source</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">citation_last_checked</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t xml:space="preserve">official_profile_url</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">email</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">notes</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
         <is>
           <t xml:space="preserve">last_verified</t>
         </is>
@@ -442,12 +625,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Department Name</t>
+          <t xml:space="preserve">Information Systems Science</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Professor Name</t>
+          <t xml:space="preserve">Jukka Heikkila</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -457,40 +640,132 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Research Area 1; Research Area 2</t>
+          <t xml:space="preserve">Information systems governance; Enterprise architecture; Business modelling</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.researchgate.net/profile/Jukka-Heikkilae</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://scholar.google.fi/citations?hl=en&amp;user=iLLaVWEAAAAJ&amp;view_op=list_works&amp;sortby=pubdate</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Turku staff profile</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.utu.fi/en/people/jukka-heikkila</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jups@utu.fi</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Turku profile publishes direct Google Scholar and ResearchGate links in profile text.</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Turku</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Health Technology</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Antti Airola</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Associate Professor</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Artificial intelligence; Data analytics; Machine learning; Health technology</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.utu.fi/en</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100+</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="J3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Turku staff profile biography</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.utu.fi/en/people/antti-airola</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ajairo@utu.fi</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The official profile states that he has co-authored over 100 peer-reviewed articles and links Google Scholar and ResearchGate profiles from the page.</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-03-14</t>
         </is>

--- a/excel/universities/university-of-turku.xlsx
+++ b/excel/universities/university-of-turku.xlsx
@@ -20,7 +20,8 @@
     <sheet name="UniversityInfo" sheetId="1" r:id="rId1"/>
     <sheet name="Deadlines" sheetId="2" r:id="rId2"/>
     <sheet name="Documents" sheetId="3" r:id="rId3"/>
-    <sheet name="Professors" sheetId="4" r:id="rId4"/>
+    <sheet name="Departments" sheetId="4" r:id="rId4"/>
+    <sheet name="Professors" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -537,6 +538,956 @@
 
 <file path=xl\worksheets\sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I20"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">university_name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unit_type</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unit_name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parent_unit</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">campus_or_city</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">focus_areas</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">official_url</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">notes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">last_verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Turku</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Education</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turku</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Education</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.utu.fi/en/university/faculties</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculties page.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Turku</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Humanities</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turku</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Humanities</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.utu.fi/en/university/faculties</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculties page.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Turku</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Law</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turku</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Law</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.utu.fi/en/university/faculties</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculties page.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Turku</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Medicine</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turku</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medicine</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.utu.fi/en/university/faculties</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculties page.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Turku</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Science</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turku</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Science; Data science; Mathematics; Physics</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.utu.fi/en/university/faculties</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculties page.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Turku</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Biology</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Science</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turku</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Biology</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.utu.fi/en/university/faculties/faculty-of-science</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listed on official faculty page.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Turku</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Biodiversity Unit</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Science</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turku</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Biodiversity</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.utu.fi/en/university/faculties/faculty-of-science</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listed on official faculty page.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Turku</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Chemistry</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Science</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turku</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chemistry</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.utu.fi/en/university/faculties/faculty-of-science</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listed on official faculty page.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Turku</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Computing</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Science</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turku</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Computing</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.utu.fi/en/university/faculties/faculty-of-science</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listed on official faculty page.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Turku</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Geography and Geology</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Science</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turku</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Geography; Geology</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.utu.fi/en/university/faculties/faculty-of-science</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listed on official faculty page.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Turku</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Learning Analytics</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Science</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turku</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Learning analytics</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.utu.fi/en/university/faculties/faculty-of-science</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listed on official faculty page.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Turku</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Mathematics and Statistics</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Science</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turku</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mathematics; Statistics</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.utu.fi/en/university/faculties/faculty-of-science</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listed on official faculty page.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Turku</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Physics and Astronomy</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Science</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turku</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Physics; Astronomy</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.utu.fi/en/university/faculties/faculty-of-science</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listed on official faculty page.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Turku</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turku School of Economics</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turku</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Economics; Business</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.utu.fi/en/university/faculties</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculties page.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Turku</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Social Sciences</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turku</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Social sciences</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.utu.fi/en/university/faculties</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculties page.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Turku</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Technology</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turku</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Engineering; Computing; Biotechnology</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.utu.fi/en/university/faculties</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculties page.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Turku</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Computing</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Technology</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turku</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Computing</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.utu.fi/en/university/faculties/faculty-of-technology</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listed on official faculty page.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Turku</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Biotechnology</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Technology</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turku</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Biotechnology</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.utu.fi/en/university/faculties/faculty-of-technology</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listed on official faculty page.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Turku</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Mechanical and Materials Engineering</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Technology</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turku</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mechanical engineering; Materials engineering</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.utu.fi/en/university/faculties/faculty-of-technology</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listed on official faculty page.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl\worksheets\sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:O3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
